--- a/artfynd/A 23067-2025 artfynd.xlsx
+++ b/artfynd/A 23067-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128463023</v>
       </c>
       <c r="B2" t="n">
-        <v>57670</v>
+        <v>57682</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 23067-2025 artfynd.xlsx
+++ b/artfynd/A 23067-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128463023</v>
       </c>
       <c r="B2" t="n">
-        <v>57682</v>
+        <v>57686</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 23067-2025 artfynd.xlsx
+++ b/artfynd/A 23067-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128463023</v>
       </c>
       <c r="B2" t="n">
-        <v>57686</v>
+        <v>57713</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 23067-2025 artfynd.xlsx
+++ b/artfynd/A 23067-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128463023</v>
       </c>
       <c r="B2" t="n">
-        <v>57713</v>
+        <v>57717</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 23067-2025 artfynd.xlsx
+++ b/artfynd/A 23067-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128463023</v>
       </c>
       <c r="B2" t="n">
-        <v>57717</v>
+        <v>57720</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
